--- a/resources/table/preset.xlsx
+++ b/resources/table/preset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791B1356-B5BA-4171-94DC-92EAF19B5CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA613AC0-3F3E-4998-98E1-E1F802A4D955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-135" windowWidth="38640" windowHeight="21120" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="preset" sheetId="7" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,14 +39,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sex</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>weapon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -125,6 +117,9 @@
   <si>
     <t>RIDING</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GENDER</t>
   </si>
 </sst>
 </file>
@@ -187,7 +182,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -203,7 +198,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -512,37 +507,37 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -550,37 +545,37 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -626,7 +621,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -653,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -661,7 +656,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -682,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -690,7 +685,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
@@ -711,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -719,7 +714,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
@@ -740,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/resources/table/preset.xlsx
+++ b/resources/table/preset.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA613AC0-3F3E-4998-98E1-E1F802A4D955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA835BFC-4D98-4F0E-AC43-A173A2352D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="38280" yWindow="-135" windowWidth="38640" windowHeight="21120" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="preset" sheetId="7" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -120,6 +120,10 @@
   </si>
   <si>
     <t>GENDER</t>
+  </si>
+  <si>
+    <t>gender</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -182,7 +186,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -198,7 +202,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -507,7 +511,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>14</v>
